--- a/reports/summary_report.xlsx
+++ b/reports/summary_report.xlsx
@@ -453,7 +453,7 @@
         <v>44</v>
       </c>
       <c r="D2" t="n">
-        <v>1623</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="3">
